--- a/PIF HOME LOAN/DL1.xlsx
+++ b/PIF HOME LOAN/DL1.xlsx
@@ -413,248 +413,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>AGENT_NAME</t>
+          <t>ACC_TYPE</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CLIENT_EMAIL</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>C_PHONE</t>
+          <t>DF_2926</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>C_TEL</t>
+          <t>DL_ADDRESS</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>DF_2926</t>
+          <t>LEADS_ACCTNO</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>DL_ADDRESS</t>
+          <t>LEADS_CHCODE</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>DOC_CODE</t>
+          <t>LEADS_CHNAME</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>D_PHONE</t>
+          <t>LEADS_ENDO_DATE</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>D_TEL</t>
+          <t>ACCT_TRANS_CODE</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>LEADS_ACCTNO</t>
+          <t>FINAL_AREA</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>LEADS_CHCODE</t>
+          <t>ADDRESS_TYPE</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>LEADS_CHNAME</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>LEADS_ENDO_DATE</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>MAIN_OFFICE_ADDRESS</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>M_PHONE</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>M_TEL</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>P_PHONE</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>P_TEL</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ACCT_TRANS_CODE</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>AGENT_CODE</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>CLIENT_NAME</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>DF_1767</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>DF_2782</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>DF_2784</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>DF_2788</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>DF_2789</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>DF_2790</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>DF_3391</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>DF_3392</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>DF_3393</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>DF_3394</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>DF_3395</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>DF_3455</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>DF_3456</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>DF_3457</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>DF_3458</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>DF_3459</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>DF_5852</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>DF_5853</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>DF_5854</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>DF_5855</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>DF_5856</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>DL_ADDRESS_TYPE_FULL</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
           <t>DL_TYPE</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>LEADS_CYCLE</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>LEADS_PLACEMENT</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>FINAL_AREA</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>ADDRESS_TYPE</t>
         </is>
       </c>
     </row>

--- a/PIF HOME LOAN/DL1.xlsx
+++ b/PIF HOME LOAN/DL1.xlsx
@@ -413,68 +413,248 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ACC_TYPE</t>
+          <t>AGENT_NAME</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CLIENT</t>
+          <t>CLIENT_EMAIL</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>C_PHONE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C_TEL</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>DF_2926</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>DL_ADDRESS</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>DOC_CODE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D_PHONE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>D_TEL</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>LEADS_ACCTNO</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>LEADS_CHCODE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>LEADS_CHNAME</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>LEADS_ENDO_DATE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>MAIN_OFFICE_ADDRESS</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>M_PHONE</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>M_TEL</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>P_PHONE</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>P_TEL</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>ACCT_TRANS_CODE</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>AGENT_CODE</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>CLIENT_NAME</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>DF_1767</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>DF_2782</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>DF_2784</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>DF_2788</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>DF_2789</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>DF_2790</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>DF_3391</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>DF_3392</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>DF_3393</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>DF_3394</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>DF_3395</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>DF_3455</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>DF_3456</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>DF_3457</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>DF_3458</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>DF_3459</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>DF_5852</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>DF_5853</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>DF_5854</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>DF_5855</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>DF_5856</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>DL_ADDRESS_TYPE_FULL</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>DL_TYPE</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>LEADS_CYCLE</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>LEADS_PLACEMENT</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>FINAL_AREA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>ADDRESS_TYPE</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>DL_TYPE</t>
         </is>
       </c>
     </row>
